--- a/public/downloads/project-finance-model.xlsx
+++ b/public/downloads/project-finance-model.xlsx
@@ -55,7 +55,7 @@
     <t>4. Run a P90 case: reduce specific yield by 7% but keep the debt sized on P50 (copy the debt amount as a value into a new input). What is the minimum DSCR? Would a 1.10x lock-up covenant trip?</t>
   </si>
   <si>
-    <t>5. Add a 0.5%/yr tariff indexation and compare the equity IRR to a flat tariff with the same levelized value.</t>
+    <t>5. Add a 0.5%/yr tariff indexation (Inputs). Record equity IRR (about 11.2%) and minimum DSCR (about 1.36x). Why does indexation raise both while the gearing cap still binds? What would the offtaker pay for it in levelized terms (use tariff-bid-evaluation.xlsx)?</t>
   </si>
   <si>
     <t>DISCLAIMER</t>
